--- a/Function 7/evals.xlsx
+++ b/Function 7/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AFFEDBF-374E-4665-BFD2-0BF781C7D4F4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA81B46A-A051-408F-84DE-912476BA5A14}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -95,10 +95,10 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -388,286 +388,300 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2" t="s">
+      <c r="I2" s="3"/>
+      <c r="J2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2" t="s">
+      <c r="K2" s="3"/>
+      <c r="L2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="3"/>
-      <c r="N2" s="2" t="s">
+      <c r="M2" s="2"/>
+      <c r="N2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="3"/>
-      <c r="P2" s="2" t="s">
+      <c r="O2" s="2"/>
+      <c r="P2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="3"/>
+      <c r="Q2" s="2"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="2">
+      <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3">
+      <c r="C3" s="3"/>
+      <c r="D3" s="2">
         <v>0</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2">
         <v>4.0108999999999999E-2</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="2"/>
       <c r="H3" s="4">
         <v>0.64410999999999996</v>
       </c>
       <c r="I3" s="4"/>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <v>0.120268</v>
       </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3">
+      <c r="K3" s="2"/>
+      <c r="L3" s="2">
         <v>0.35586299999999998</v>
       </c>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3">
+      <c r="M3" s="2"/>
+      <c r="N3" s="2">
         <v>0.87413600000000002</v>
       </c>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3">
+      <c r="O3" s="2"/>
+      <c r="P3" s="2">
         <v>1.39427779979913</v>
       </c>
-      <c r="Q3" s="3"/>
+      <c r="Q3" s="2"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B4" s="2">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="3">
+      <c r="C4" s="3"/>
+      <c r="D4" s="2">
         <v>0</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3">
+      <c r="E4" s="2"/>
+      <c r="F4" s="2">
         <v>0.28961338659042302</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3">
+      <c r="G4" s="2"/>
+      <c r="H4" s="2">
         <v>0</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3">
+      <c r="I4" s="2"/>
+      <c r="J4" s="2">
         <v>6.13308944438598E-2</v>
       </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3">
+      <c r="K4" s="2"/>
+      <c r="L4" s="2">
         <v>0.34585898347106497</v>
       </c>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3">
+      <c r="M4" s="2"/>
+      <c r="N4" s="2">
         <v>1</v>
       </c>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3">
+      <c r="O4" s="2"/>
+      <c r="P4" s="2">
         <v>0.45343011622374302</v>
       </c>
-      <c r="Q4" s="3"/>
+      <c r="Q4" s="2"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="2">
+      <c r="B5" s="3">
         <v>3</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="3">
+      <c r="C5" s="3"/>
+      <c r="D5" s="2">
         <v>0</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3">
+      <c r="E5" s="2"/>
+      <c r="F5" s="2">
         <v>8.0709819324134596E-2</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3">
+      <c r="G5" s="2"/>
+      <c r="H5" s="2">
         <v>0.69429131436978797</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3">
+      <c r="I5" s="2"/>
+      <c r="J5" s="2">
         <v>7.2853222028172807E-2</v>
       </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3">
+      <c r="K5" s="2"/>
+      <c r="L5" s="2">
         <v>0.36239023356917699</v>
       </c>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3">
+      <c r="M5" s="2"/>
+      <c r="N5" s="2">
         <v>0.74847589206358001</v>
       </c>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3">
+      <c r="O5" s="2"/>
+      <c r="P5" s="2">
         <v>1.55434315265553</v>
       </c>
-      <c r="Q5" s="3"/>
+      <c r="Q5" s="2"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <v>4</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="3">
+      <c r="C6" s="3"/>
+      <c r="D6" s="2">
         <v>0</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3">
+      <c r="E6" s="2"/>
+      <c r="F6" s="2">
         <v>0.42931845594636298</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3">
+      <c r="G6" s="2"/>
+      <c r="H6" s="2">
         <v>0.83076178581695104</v>
       </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3">
+      <c r="I6" s="2"/>
+      <c r="J6" s="2">
         <v>0.16965226103521699</v>
       </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3">
+      <c r="K6" s="2"/>
+      <c r="L6" s="2">
         <v>0.38090490400002902</v>
       </c>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3">
+      <c r="M6" s="2"/>
+      <c r="N6" s="2">
         <v>0.78712442114333403</v>
       </c>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2">
+        <v>1.33614435553374</v>
+      </c>
+      <c r="Q6" s="2"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>5</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2">
+        <v>0.42242649332848198</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2">
+        <v>0.206257083288932</v>
+      </c>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2">
+        <v>0.36942492544856198</v>
+      </c>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2">
+        <v>0.76249972472752303</v>
+      </c>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -675,6 +689,70 @@
     </row>
   </sheetData>
   <mergeCells count="76">
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H13:I13"/>
     <mergeCell ref="J7:K7"/>
     <mergeCell ref="L7:M7"/>
     <mergeCell ref="N7:O7"/>
@@ -687,70 +765,6 @@
     <mergeCell ref="P6:Q6"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="L5:M5"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="N2:O2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 7/evals.xlsx
+++ b/Function 7/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA81B46A-A051-408F-84DE-912476BA5A14}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55FA9A28-193F-4654-92EF-AF5E3CE78C2E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -95,10 +95,10 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -388,307 +388,395 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3" t="s">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3" t="s">
+      <c r="K2" s="2"/>
+      <c r="L2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="2"/>
-      <c r="N2" s="3" t="s">
+      <c r="M2" s="3"/>
+      <c r="N2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="2"/>
-      <c r="P2" s="3" t="s">
+      <c r="O2" s="3"/>
+      <c r="P2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="2"/>
+      <c r="Q2" s="3"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>1</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2">
+      <c r="C3" s="2"/>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3">
         <v>4.0108999999999999E-2</v>
       </c>
-      <c r="G3" s="2"/>
+      <c r="G3" s="3"/>
       <c r="H3" s="4">
         <v>0.64410999999999996</v>
       </c>
       <c r="I3" s="4"/>
-      <c r="J3" s="2">
+      <c r="J3" s="3">
         <v>0.120268</v>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2">
+      <c r="K3" s="3"/>
+      <c r="L3" s="3">
         <v>0.35586299999999998</v>
       </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2">
+      <c r="M3" s="3"/>
+      <c r="N3" s="3">
         <v>0.87413600000000002</v>
       </c>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2">
+      <c r="O3" s="3"/>
+      <c r="P3" s="3">
         <v>1.39427779979913</v>
       </c>
-      <c r="Q3" s="2"/>
+      <c r="Q3" s="3"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>2</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2">
+      <c r="C4" s="2"/>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3">
         <v>0.28961338659042302</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2">
+      <c r="G4" s="3"/>
+      <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3">
         <v>6.13308944438598E-2</v>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2">
+      <c r="K4" s="3"/>
+      <c r="L4" s="3">
         <v>0.34585898347106497</v>
       </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2">
+      <c r="M4" s="3"/>
+      <c r="N4" s="3">
         <v>1</v>
       </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2">
+      <c r="O4" s="3"/>
+      <c r="P4" s="3">
         <v>0.45343011622374302</v>
       </c>
-      <c r="Q4" s="2"/>
+      <c r="Q4" s="3"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>3</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2">
+      <c r="C5" s="2"/>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3">
         <v>8.0709819324134596E-2</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2">
+      <c r="G5" s="3"/>
+      <c r="H5" s="3">
         <v>0.69429131436978797</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2">
+      <c r="I5" s="3"/>
+      <c r="J5" s="3">
         <v>7.2853222028172807E-2</v>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2">
+      <c r="K5" s="3"/>
+      <c r="L5" s="3">
         <v>0.36239023356917699</v>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2">
+      <c r="M5" s="3"/>
+      <c r="N5" s="3">
         <v>0.74847589206358001</v>
       </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2">
+      <c r="O5" s="3"/>
+      <c r="P5" s="3">
         <v>1.55434315265553</v>
       </c>
-      <c r="Q5" s="2"/>
+      <c r="Q5" s="3"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>4</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2">
+      <c r="C6" s="2"/>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3">
         <v>0.42931845594636298</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3">
         <v>0.83076178581695104</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2">
+      <c r="I6" s="3"/>
+      <c r="J6" s="3">
         <v>0.16965226103521699</v>
       </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2">
+      <c r="K6" s="3"/>
+      <c r="L6" s="3">
         <v>0.38090490400002902</v>
       </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2">
+      <c r="M6" s="3"/>
+      <c r="N6" s="3">
         <v>0.78712442114333403</v>
       </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2">
+      <c r="O6" s="3"/>
+      <c r="P6" s="3">
         <v>1.33614435553374</v>
       </c>
-      <c r="Q6" s="2"/>
+      <c r="Q6" s="3"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" s="2">
         <v>5</v>
       </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2">
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3">
         <v>0.42242649332848198</v>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2">
+      <c r="I7" s="3"/>
+      <c r="J7" s="3">
         <v>0.206257083288932</v>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2">
+      <c r="K7" s="3"/>
+      <c r="L7" s="3">
         <v>0.36942492544856198</v>
       </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2">
+      <c r="M7" s="3"/>
+      <c r="N7" s="3">
         <v>0.76249972472752303</v>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3">
+        <v>2.1665086099757902</v>
+      </c>
+      <c r="Q7" s="3"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B8" s="2"/>
+      <c r="B8" s="2">
+        <v>6</v>
+      </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3">
+        <v>0.426408951454678</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3">
+        <v>0.27180790722301601</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3">
+        <v>0.34758937274031698</v>
+      </c>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3">
+        <v>0.74913190087147996</v>
+      </c>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="76">
+  <mergeCells count="80">
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="L4:M4"/>
@@ -701,70 +789,6 @@
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:M5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 7/evals.xlsx
+++ b/Function 7/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55FA9A28-193F-4654-92EF-AF5E3CE78C2E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62FD2C7B-BDCE-4134-AA88-9ECA9B9DEF49}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -95,10 +95,10 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -388,320 +388,320 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2" t="s">
+      <c r="I2" s="3"/>
+      <c r="J2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2" t="s">
+      <c r="K2" s="3"/>
+      <c r="L2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="3"/>
-      <c r="N2" s="2" t="s">
+      <c r="M2" s="2"/>
+      <c r="N2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="3"/>
-      <c r="P2" s="2" t="s">
+      <c r="O2" s="2"/>
+      <c r="P2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="3"/>
+      <c r="Q2" s="2"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="2">
+      <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3">
+      <c r="C3" s="3"/>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2">
         <v>4.0108999999999999E-2</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="2"/>
       <c r="H3" s="4">
         <v>0.64410999999999996</v>
       </c>
       <c r="I3" s="4"/>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <v>0.120268</v>
       </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3">
+      <c r="K3" s="2"/>
+      <c r="L3" s="2">
         <v>0.35586299999999998</v>
       </c>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3">
+      <c r="M3" s="2"/>
+      <c r="N3" s="2">
         <v>0.87413600000000002</v>
       </c>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3">
+      <c r="O3" s="2"/>
+      <c r="P3" s="2">
         <v>1.39427779979913</v>
       </c>
-      <c r="Q3" s="3"/>
+      <c r="Q3" s="2"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B4" s="2">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="3">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3">
+      <c r="C4" s="3"/>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2">
         <v>0.28961338659042302</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3">
+      <c r="G4" s="2"/>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2">
         <v>6.13308944438598E-2</v>
       </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3">
+      <c r="K4" s="2"/>
+      <c r="L4" s="2">
         <v>0.34585898347106497</v>
       </c>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3">
+      <c r="M4" s="2"/>
+      <c r="N4" s="2">
         <v>1</v>
       </c>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3">
+      <c r="O4" s="2"/>
+      <c r="P4" s="2">
         <v>0.45343011622374302</v>
       </c>
-      <c r="Q4" s="3"/>
+      <c r="Q4" s="2"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="2">
+      <c r="B5" s="3">
         <v>3</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="3">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3">
+      <c r="C5" s="3"/>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2">
         <v>8.0709819324134596E-2</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3">
+      <c r="G5" s="2"/>
+      <c r="H5" s="2">
         <v>0.69429131436978797</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3">
+      <c r="I5" s="2"/>
+      <c r="J5" s="2">
         <v>7.2853222028172807E-2</v>
       </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3">
+      <c r="K5" s="2"/>
+      <c r="L5" s="2">
         <v>0.36239023356917699</v>
       </c>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3">
+      <c r="M5" s="2"/>
+      <c r="N5" s="2">
         <v>0.74847589206358001</v>
       </c>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3">
+      <c r="O5" s="2"/>
+      <c r="P5" s="2">
         <v>1.55434315265553</v>
       </c>
-      <c r="Q5" s="3"/>
+      <c r="Q5" s="2"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <v>4</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="3">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3">
+      <c r="C6" s="3"/>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2">
         <v>0.42931845594636298</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3">
+      <c r="G6" s="2"/>
+      <c r="H6" s="2">
         <v>0.83076178581695104</v>
       </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3">
+      <c r="I6" s="2"/>
+      <c r="J6" s="2">
         <v>0.16965226103521699</v>
       </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3">
+      <c r="K6" s="2"/>
+      <c r="L6" s="2">
         <v>0.38090490400002902</v>
       </c>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3">
+      <c r="M6" s="2"/>
+      <c r="N6" s="2">
         <v>0.78712442114333403</v>
       </c>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3">
+      <c r="O6" s="2"/>
+      <c r="P6" s="2">
         <v>1.33614435553374</v>
       </c>
-      <c r="Q6" s="3"/>
+      <c r="Q6" s="2"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B7" s="2">
+      <c r="B7" s="3">
         <v>5</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="3">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3">
+      <c r="C7" s="3"/>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2">
         <v>0.42242649332848198</v>
       </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3">
+      <c r="I7" s="2"/>
+      <c r="J7" s="2">
         <v>0.206257083288932</v>
       </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3">
+      <c r="K7" s="2"/>
+      <c r="L7" s="2">
         <v>0.36942492544856198</v>
       </c>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3">
+      <c r="M7" s="2"/>
+      <c r="N7" s="2">
         <v>0.76249972472752303</v>
       </c>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3">
+      <c r="O7" s="2"/>
+      <c r="P7" s="2">
         <v>2.1665086099757902</v>
       </c>
-      <c r="Q7" s="3"/>
+      <c r="Q7" s="2"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B8" s="2">
+      <c r="B8" s="3">
         <v>6</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="3">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3">
+      <c r="C8" s="3"/>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2">
         <v>0.426408951454678</v>
       </c>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3">
+      <c r="I8" s="2"/>
+      <c r="J8" s="2">
         <v>0.27180790722301601</v>
       </c>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3">
+      <c r="K8" s="2"/>
+      <c r="L8" s="2">
         <v>0.34758937274031698</v>
       </c>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3">
+      <c r="M8" s="2"/>
+      <c r="N8" s="2">
         <v>0.74913190087147996</v>
       </c>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -709,32 +709,48 @@
     </row>
   </sheetData>
   <mergeCells count="80">
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
@@ -747,48 +763,32 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="P7:Q7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 7/evals.xlsx
+++ b/Function 7/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62FD2C7B-BDCE-4134-AA88-9ECA9B9DEF49}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A559E69-6B0D-4D5B-B74F-5B77D9544232}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -95,10 +95,10 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -388,327 +388,419 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3" t="s">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3" t="s">
+      <c r="K2" s="2"/>
+      <c r="L2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="2"/>
-      <c r="N2" s="3" t="s">
+      <c r="M2" s="3"/>
+      <c r="N2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="2"/>
-      <c r="P2" s="3" t="s">
+      <c r="O2" s="3"/>
+      <c r="P2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="2"/>
+      <c r="Q2" s="3"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>1</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2">
+      <c r="C3" s="2"/>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3">
         <v>4.0108999999999999E-2</v>
       </c>
-      <c r="G3" s="2"/>
+      <c r="G3" s="3"/>
       <c r="H3" s="4">
         <v>0.64410999999999996</v>
       </c>
       <c r="I3" s="4"/>
-      <c r="J3" s="2">
+      <c r="J3" s="3">
         <v>0.120268</v>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2">
+      <c r="K3" s="3"/>
+      <c r="L3" s="3">
         <v>0.35586299999999998</v>
       </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2">
+      <c r="M3" s="3"/>
+      <c r="N3" s="3">
         <v>0.87413600000000002</v>
       </c>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2">
+      <c r="O3" s="3"/>
+      <c r="P3" s="3">
         <v>1.39427779979913</v>
       </c>
-      <c r="Q3" s="2"/>
+      <c r="Q3" s="3"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>2</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2">
+      <c r="C4" s="2"/>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3">
         <v>0.28961338659042302</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2">
+      <c r="G4" s="3"/>
+      <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3">
         <v>6.13308944438598E-2</v>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2">
+      <c r="K4" s="3"/>
+      <c r="L4" s="3">
         <v>0.34585898347106497</v>
       </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2">
+      <c r="M4" s="3"/>
+      <c r="N4" s="3">
         <v>1</v>
       </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2">
+      <c r="O4" s="3"/>
+      <c r="P4" s="3">
         <v>0.45343011622374302</v>
       </c>
-      <c r="Q4" s="2"/>
+      <c r="Q4" s="3"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>3</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2">
+      <c r="C5" s="2"/>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3">
         <v>8.0709819324134596E-2</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2">
+      <c r="G5" s="3"/>
+      <c r="H5" s="3">
         <v>0.69429131436978797</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2">
+      <c r="I5" s="3"/>
+      <c r="J5" s="3">
         <v>7.2853222028172807E-2</v>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2">
+      <c r="K5" s="3"/>
+      <c r="L5" s="3">
         <v>0.36239023356917699</v>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2">
+      <c r="M5" s="3"/>
+      <c r="N5" s="3">
         <v>0.74847589206358001</v>
       </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2">
+      <c r="O5" s="3"/>
+      <c r="P5" s="3">
         <v>1.55434315265553</v>
       </c>
-      <c r="Q5" s="2"/>
+      <c r="Q5" s="3"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>4</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2">
+      <c r="C6" s="2"/>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3">
         <v>0.42931845594636298</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3">
         <v>0.83076178581695104</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2">
+      <c r="I6" s="3"/>
+      <c r="J6" s="3">
         <v>0.16965226103521699</v>
       </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2">
+      <c r="K6" s="3"/>
+      <c r="L6" s="3">
         <v>0.38090490400002902</v>
       </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2">
+      <c r="M6" s="3"/>
+      <c r="N6" s="3">
         <v>0.78712442114333403</v>
       </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2">
+      <c r="O6" s="3"/>
+      <c r="P6" s="3">
         <v>1.33614435553374</v>
       </c>
-      <c r="Q6" s="2"/>
+      <c r="Q6" s="3"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>5</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2">
+      <c r="C7" s="2"/>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3">
         <v>0.42242649332848198</v>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2">
+      <c r="I7" s="3"/>
+      <c r="J7" s="3">
         <v>0.206257083288932</v>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2">
+      <c r="K7" s="3"/>
+      <c r="L7" s="3">
         <v>0.36942492544856198</v>
       </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2">
+      <c r="M7" s="3"/>
+      <c r="N7" s="3">
         <v>0.76249972472752303</v>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2">
+      <c r="O7" s="3"/>
+      <c r="P7" s="3">
         <v>2.1665086099757902</v>
       </c>
-      <c r="Q7" s="2"/>
+      <c r="Q7" s="3"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>6</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2">
+      <c r="C8" s="2"/>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3">
         <v>0.426408951454678</v>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2">
+      <c r="I8" s="3"/>
+      <c r="J8" s="3">
         <v>0.27180790722301601</v>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2">
+      <c r="K8" s="3"/>
+      <c r="L8" s="3">
         <v>0.34758937274031698</v>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2">
+      <c r="M8" s="3"/>
+      <c r="N8" s="3">
         <v>0.74913190087147996</v>
       </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3">
+        <v>2.3917221178118799</v>
+      </c>
+      <c r="Q8" s="3"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
+      <c r="B9" s="2">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3">
+        <v>0.49191789534416003</v>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3">
+        <v>0.32159452667306399</v>
+      </c>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3">
+        <v>0.35095097771923101</v>
+      </c>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3">
+        <v>0.71218468267868695</v>
+      </c>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="80">
+  <mergeCells count="84">
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="L4:M4"/>
@@ -721,74 +813,6 @@
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="P7:Q7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 7/evals.xlsx
+++ b/Function 7/evals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A559E69-6B0D-4D5B-B74F-5B77D9544232}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBC68C6-48BB-431F-89A3-4A59A6C6F033}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -95,10 +95,10 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -385,358 +385,438 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:Q14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2" t="s">
+      <c r="I2" s="3"/>
+      <c r="J2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2" t="s">
+      <c r="K2" s="3"/>
+      <c r="L2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="3"/>
-      <c r="N2" s="2" t="s">
+      <c r="M2" s="2"/>
+      <c r="N2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="3"/>
-      <c r="P2" s="2" t="s">
+      <c r="O2" s="2"/>
+      <c r="P2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="3"/>
-    </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="2">
+      <c r="Q2" s="2"/>
+    </row>
+    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3">
+      <c r="C3" s="3"/>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2">
         <v>4.0108999999999999E-2</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="2"/>
       <c r="H3" s="4">
         <v>0.64410999999999996</v>
       </c>
       <c r="I3" s="4"/>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <v>0.120268</v>
       </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3">
+      <c r="K3" s="2"/>
+      <c r="L3" s="2">
         <v>0.35586299999999998</v>
       </c>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3">
+      <c r="M3" s="2"/>
+      <c r="N3" s="2">
         <v>0.87413600000000002</v>
       </c>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3">
+      <c r="O3" s="2"/>
+      <c r="P3" s="2">
         <v>1.39427779979913</v>
       </c>
-      <c r="Q3" s="3"/>
-    </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B4" s="2">
+      <c r="Q3" s="2"/>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="3">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3">
+      <c r="C4" s="3"/>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2">
         <v>0.28961338659042302</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3">
+      <c r="G4" s="2"/>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2">
         <v>6.13308944438598E-2</v>
       </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3">
+      <c r="K4" s="2"/>
+      <c r="L4" s="2">
         <v>0.34585898347106497</v>
       </c>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3">
+      <c r="M4" s="2"/>
+      <c r="N4" s="2">
         <v>1</v>
       </c>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3">
+      <c r="O4" s="2"/>
+      <c r="P4" s="2">
         <v>0.45343011622374302</v>
       </c>
-      <c r="Q4" s="3"/>
-    </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="2">
+      <c r="Q4" s="2"/>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B5" s="3">
         <v>3</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="3">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3">
+      <c r="C5" s="3"/>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2">
         <v>8.0709819324134596E-2</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3">
+      <c r="G5" s="2"/>
+      <c r="H5" s="2">
         <v>0.69429131436978797</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3">
+      <c r="I5" s="2"/>
+      <c r="J5" s="2">
         <v>7.2853222028172807E-2</v>
       </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3">
+      <c r="K5" s="2"/>
+      <c r="L5" s="2">
         <v>0.36239023356917699</v>
       </c>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3">
+      <c r="M5" s="2"/>
+      <c r="N5" s="2">
         <v>0.74847589206358001</v>
       </c>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3">
+      <c r="O5" s="2"/>
+      <c r="P5" s="2">
         <v>1.55434315265553</v>
       </c>
-      <c r="Q5" s="3"/>
-    </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="2">
+      <c r="Q5" s="2"/>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B6" s="3">
         <v>4</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="3">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3">
+      <c r="C6" s="3"/>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2">
         <v>0.42931845594636298</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3">
+      <c r="G6" s="2"/>
+      <c r="H6" s="2">
         <v>0.83076178581695104</v>
       </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3">
+      <c r="I6" s="2"/>
+      <c r="J6" s="2">
         <v>0.16965226103521699</v>
       </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3">
+      <c r="K6" s="2"/>
+      <c r="L6" s="2">
         <v>0.38090490400002902</v>
       </c>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3">
+      <c r="M6" s="2"/>
+      <c r="N6" s="2">
         <v>0.78712442114333403</v>
       </c>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3">
+      <c r="O6" s="2"/>
+      <c r="P6" s="2">
         <v>1.33614435553374</v>
       </c>
-      <c r="Q6" s="3"/>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B7" s="2">
+      <c r="Q6" s="2"/>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B7" s="3">
         <v>5</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="3">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3">
+      <c r="C7" s="3"/>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2">
         <v>0.42242649332848198</v>
       </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3">
+      <c r="I7" s="2"/>
+      <c r="J7" s="2">
         <v>0.206257083288932</v>
       </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3">
+      <c r="K7" s="2"/>
+      <c r="L7" s="2">
         <v>0.36942492544856198</v>
       </c>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3">
+      <c r="M7" s="2"/>
+      <c r="N7" s="2">
         <v>0.76249972472752303</v>
       </c>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3">
+      <c r="O7" s="2"/>
+      <c r="P7" s="2">
         <v>2.1665086099757902</v>
       </c>
-      <c r="Q7" s="3"/>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B8" s="2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B8" s="3">
         <v>6</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="3">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3">
+      <c r="C8" s="3"/>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2">
         <v>0.426408951454678</v>
       </c>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3">
+      <c r="I8" s="2"/>
+      <c r="J8" s="2">
         <v>0.27180790722301601</v>
       </c>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3">
+      <c r="K8" s="2"/>
+      <c r="L8" s="2">
         <v>0.34758937274031698</v>
       </c>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3">
+      <c r="M8" s="2"/>
+      <c r="N8" s="2">
         <v>0.74913190087147996</v>
       </c>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3">
+      <c r="O8" s="2"/>
+      <c r="P8" s="2">
         <v>2.3917221178118799</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B9" s="2">
+      <c r="Q8" s="2"/>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B9" s="3">
         <v>7</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="3">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3">
+      <c r="C9" s="3"/>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2">
         <v>0.49191789534416003</v>
       </c>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3">
+      <c r="I9" s="2"/>
+      <c r="J9" s="2">
         <v>0.32159452667306399</v>
       </c>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3">
+      <c r="K9" s="2"/>
+      <c r="L9" s="2">
         <v>0.35095097771923101</v>
       </c>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3">
+      <c r="M9" s="2"/>
+      <c r="N9" s="2">
         <v>0.71218468267868695</v>
       </c>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B10" s="3"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2">
+        <v>2.4554838323913799</v>
+      </c>
+      <c r="Q9" s="2"/>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B10" s="3">
+        <v>8</v>
+      </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-    </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2">
+        <v>0.38612599363609401</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2">
+        <v>0.31697341195039502</v>
+      </c>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2">
+        <v>0.33867434799301199</v>
+      </c>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2">
+        <v>0.70327955630146899</v>
+      </c>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="84">
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="J8:K8"/>
+  <mergeCells count="88">
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H13:I13"/>
     <mergeCell ref="J7:K7"/>
     <mergeCell ref="L7:M7"/>
     <mergeCell ref="N7:O7"/>
@@ -749,70 +829,14 @@
     <mergeCell ref="P6:Q6"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="L5:M5"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="J8:K8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 7/evals.xlsx
+++ b/Function 7/evals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBC68C6-48BB-431F-89A3-4A59A6C6F033}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA05ACB-82FD-4BE3-93E0-4A68C70E6E9D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -385,9 +385,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:Q14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -421,7 +421,7 @@
       </c>
       <c r="Q2" s="2"/>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B3" s="3">
         <v>1</v>
       </c>
@@ -455,7 +455,7 @@
       </c>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B4" s="3">
         <v>2</v>
       </c>
@@ -489,7 +489,7 @@
       </c>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
         <v>3</v>
       </c>
@@ -523,7 +523,7 @@
       </c>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
         <v>4</v>
       </c>
@@ -557,7 +557,7 @@
       </c>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" s="3">
         <v>5</v>
       </c>
@@ -591,7 +591,7 @@
       </c>
       <c r="Q7" s="2"/>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="3">
         <v>6</v>
       </c>
@@ -625,7 +625,7 @@
       </c>
       <c r="Q8" s="2"/>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" s="3">
         <v>7</v>
       </c>
@@ -659,7 +659,7 @@
       </c>
       <c r="Q9" s="2"/>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="3">
         <v>8</v>
       </c>
@@ -688,52 +688,84 @@
         <v>0.70327955630146899</v>
       </c>
       <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
+      <c r="P10" s="2">
+        <v>2.4709723469157598</v>
+      </c>
       <c r="Q10" s="2"/>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B11" s="3">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
       <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="H11" s="2">
+        <v>0.384347832011811</v>
+      </c>
       <c r="I11" s="2"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-    </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="J11" s="2">
+        <v>0.33550441466605302</v>
+      </c>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2">
+        <v>0.34935696999064397</v>
+      </c>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2">
+        <v>0.71889891147558604</v>
+      </c>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B12" s="3">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-    </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B13" s="3">
+        <v>11</v>
+      </c>
+      <c r="C13" s="3"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -748,7 +780,91 @@
       <c r="M14" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="88">
+  <mergeCells count="100">
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
     <mergeCell ref="P10:Q10"/>
     <mergeCell ref="N10:O10"/>
     <mergeCell ref="L10:M10"/>
@@ -765,78 +881,6 @@
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="J8:K8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 7/evals.xlsx
+++ b/Function 7/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA05ACB-82FD-4BE3-93E0-4A68C70E6E9D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13ED9EAE-F70E-4943-BA91-F83E628EB7E8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -781,90 +781,6 @@
     </row>
   </sheetData>
   <mergeCells count="100">
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
     <mergeCell ref="P10:Q10"/>
     <mergeCell ref="N10:O10"/>
     <mergeCell ref="L10:M10"/>
@@ -881,6 +797,90 @@
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="N2:O2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 7/evals.xlsx
+++ b/Function 7/evals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13ED9EAE-F70E-4943-BA91-F83E628EB7E8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4940ADAE-F6F9-44E8-9A37-4D33EA1D8FD8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -385,9 +385,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:Q14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -421,7 +421,7 @@
       </c>
       <c r="Q2" s="2"/>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
         <v>1</v>
       </c>
@@ -455,7 +455,7 @@
       </c>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B4" s="3">
         <v>2</v>
       </c>
@@ -489,7 +489,7 @@
       </c>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" s="3">
         <v>3</v>
       </c>
@@ -523,7 +523,7 @@
       </c>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B6" s="3">
         <v>4</v>
       </c>
@@ -557,7 +557,7 @@
       </c>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
         <v>5</v>
       </c>
@@ -591,7 +591,7 @@
       </c>
       <c r="Q7" s="2"/>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="3">
         <v>6</v>
       </c>
@@ -625,7 +625,7 @@
       </c>
       <c r="Q8" s="2"/>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
         <v>7</v>
       </c>
@@ -659,7 +659,7 @@
       </c>
       <c r="Q9" s="2"/>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>8</v>
       </c>
@@ -693,7 +693,7 @@
       </c>
       <c r="Q10" s="2"/>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <v>9</v>
       </c>
@@ -722,30 +722,44 @@
         <v>0.71889891147558604</v>
       </c>
       <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
+      <c r="P11" s="2">
+        <v>2.3703047996399298</v>
+      </c>
       <c r="Q11" s="2"/>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <v>10</v>
       </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="2"/>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
       <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="H12" s="2">
+        <v>0.50273361903901903</v>
+      </c>
       <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
+      <c r="J12" s="2">
+        <v>0.27430778792633997</v>
+      </c>
       <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
+      <c r="L12" s="2">
+        <v>0.32177575521011098</v>
+      </c>
       <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
+      <c r="N12" s="2">
+        <v>0.65673741494184301</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
         <v>11</v>
       </c>
@@ -765,7 +779,7 @@
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -781,6 +795,90 @@
     </row>
   </sheetData>
   <mergeCells count="100">
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
     <mergeCell ref="P10:Q10"/>
     <mergeCell ref="N10:O10"/>
     <mergeCell ref="L10:M10"/>
@@ -797,90 +895,6 @@
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P12:Q12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 7/evals.xlsx
+++ b/Function 7/evals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4940ADAE-F6F9-44E8-9A37-4D33EA1D8FD8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3FFC296-DFDA-4565-AA4A-7C177976AB8D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -92,9 +92,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -385,500 +384,440 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:Q14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3" t="s">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3" t="s">
+      <c r="K2" s="2"/>
+      <c r="L2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="2"/>
-      <c r="N2" s="3" t="s">
+      <c r="M2" s="1"/>
+      <c r="N2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="2"/>
-      <c r="P2" s="3" t="s">
+      <c r="O2" s="1"/>
+      <c r="P2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="2"/>
-    </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B3" s="3">
+      <c r="Q2" s="1"/>
+    </row>
+    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B3" s="2">
         <v>1</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2">
+      <c r="C3" s="2"/>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1">
         <v>4.0108999999999999E-2</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="4">
+      <c r="G3" s="1"/>
+      <c r="H3" s="3">
         <v>0.64410999999999996</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="2">
+      <c r="I3" s="3"/>
+      <c r="J3" s="1">
         <v>0.120268</v>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2">
+      <c r="K3" s="1"/>
+      <c r="L3" s="1">
         <v>0.35586299999999998</v>
       </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2">
+      <c r="M3" s="1"/>
+      <c r="N3" s="1">
         <v>0.87413600000000002</v>
       </c>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2">
+      <c r="O3" s="1"/>
+      <c r="P3" s="1">
         <v>1.39427779979913</v>
       </c>
-      <c r="Q3" s="2"/>
-    </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B4" s="3">
+      <c r="Q3" s="1"/>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B4" s="2">
         <v>2</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2">
+      <c r="C4" s="2"/>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1">
         <v>0.28961338659042302</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2">
+      <c r="G4" s="1"/>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1">
         <v>6.13308944438598E-2</v>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2">
+      <c r="K4" s="1"/>
+      <c r="L4" s="1">
         <v>0.34585898347106497</v>
       </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2">
+      <c r="M4" s="1"/>
+      <c r="N4" s="1">
         <v>1</v>
       </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2">
+      <c r="O4" s="1"/>
+      <c r="P4" s="1">
         <v>0.45343011622374302</v>
       </c>
-      <c r="Q4" s="2"/>
-    </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B5" s="3">
+      <c r="Q4" s="1"/>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B5" s="2">
         <v>3</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2">
+      <c r="C5" s="2"/>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1">
         <v>8.0709819324134596E-2</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2">
+      <c r="G5" s="1"/>
+      <c r="H5" s="1">
         <v>0.69429131436978797</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2">
+      <c r="I5" s="1"/>
+      <c r="J5" s="1">
         <v>7.2853222028172807E-2</v>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2">
+      <c r="K5" s="1"/>
+      <c r="L5" s="1">
         <v>0.36239023356917699</v>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2">
+      <c r="M5" s="1"/>
+      <c r="N5" s="1">
         <v>0.74847589206358001</v>
       </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2">
+      <c r="O5" s="1"/>
+      <c r="P5" s="1">
         <v>1.55434315265553</v>
       </c>
-      <c r="Q5" s="2"/>
-    </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B6" s="3">
+      <c r="Q5" s="1"/>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B6" s="2">
         <v>4</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2">
+      <c r="C6" s="2"/>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1">
         <v>0.42931845594636298</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2">
+      <c r="G6" s="1"/>
+      <c r="H6" s="1">
         <v>0.83076178581695104</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2">
+      <c r="I6" s="1"/>
+      <c r="J6" s="1">
         <v>0.16965226103521699</v>
       </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2">
+      <c r="K6" s="1"/>
+      <c r="L6" s="1">
         <v>0.38090490400002902</v>
       </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2">
+      <c r="M6" s="1"/>
+      <c r="N6" s="1">
         <v>0.78712442114333403</v>
       </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2">
+      <c r="O6" s="1"/>
+      <c r="P6" s="1">
         <v>1.33614435553374</v>
       </c>
-      <c r="Q6" s="2"/>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B7" s="3">
+      <c r="Q6" s="1"/>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B7" s="2">
         <v>5</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2">
+      <c r="C7" s="2"/>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1">
         <v>0.42242649332848198</v>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2">
+      <c r="I7" s="1"/>
+      <c r="J7" s="1">
         <v>0.206257083288932</v>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2">
+      <c r="K7" s="1"/>
+      <c r="L7" s="1">
         <v>0.36942492544856198</v>
       </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2">
+      <c r="M7" s="1"/>
+      <c r="N7" s="1">
         <v>0.76249972472752303</v>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2">
+      <c r="O7" s="1"/>
+      <c r="P7" s="1">
         <v>2.1665086099757902</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B8" s="3">
+      <c r="Q7" s="1"/>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B8" s="2">
         <v>6</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2">
+      <c r="C8" s="2"/>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1">
         <v>0.426408951454678</v>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2">
+      <c r="I8" s="1"/>
+      <c r="J8" s="1">
         <v>0.27180790722301601</v>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2">
+      <c r="K8" s="1"/>
+      <c r="L8" s="1">
         <v>0.34758937274031698</v>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2">
+      <c r="M8" s="1"/>
+      <c r="N8" s="1">
         <v>0.74913190087147996</v>
       </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2">
+      <c r="O8" s="1"/>
+      <c r="P8" s="1">
         <v>2.3917221178118799</v>
       </c>
-      <c r="Q8" s="2"/>
-    </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B9" s="3">
+      <c r="Q8" s="1"/>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B9" s="2">
         <v>7</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2">
+      <c r="C9" s="2"/>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1">
         <v>0.49191789534416003</v>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2">
+      <c r="I9" s="1"/>
+      <c r="J9" s="1">
         <v>0.32159452667306399</v>
       </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2">
+      <c r="K9" s="1"/>
+      <c r="L9" s="1">
         <v>0.35095097771923101</v>
       </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2">
+      <c r="M9" s="1"/>
+      <c r="N9" s="1">
         <v>0.71218468267868695</v>
       </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2">
+      <c r="O9" s="1"/>
+      <c r="P9" s="1">
         <v>2.4554838323913799</v>
       </c>
-      <c r="Q9" s="2"/>
-    </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B10" s="3">
+      <c r="Q9" s="1"/>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B10" s="2">
         <v>8</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2">
+      <c r="C10" s="2"/>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1">
         <v>0.38612599363609401</v>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2">
+      <c r="I10" s="1"/>
+      <c r="J10" s="1">
         <v>0.31697341195039502</v>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2">
+      <c r="K10" s="1"/>
+      <c r="L10" s="1">
         <v>0.33867434799301199</v>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2">
+      <c r="M10" s="1"/>
+      <c r="N10" s="1">
         <v>0.70327955630146899</v>
       </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2">
+      <c r="O10" s="1"/>
+      <c r="P10" s="1">
         <v>2.4709723469157598</v>
       </c>
-      <c r="Q10" s="2"/>
-    </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="3">
+      <c r="Q10" s="1"/>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B11" s="2">
         <v>9</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2">
+      <c r="C11" s="2"/>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1">
         <v>0.384347832011811</v>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2">
+      <c r="I11" s="1"/>
+      <c r="J11" s="1">
         <v>0.33550441466605302</v>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2">
+      <c r="K11" s="1"/>
+      <c r="L11" s="1">
         <v>0.34935696999064397</v>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2">
+      <c r="M11" s="1"/>
+      <c r="N11" s="1">
         <v>0.71889891147558604</v>
       </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2">
+      <c r="O11" s="1"/>
+      <c r="P11" s="1">
         <v>2.3703047996399298</v>
       </c>
-      <c r="Q11" s="2"/>
-    </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="3">
+      <c r="Q11" s="1"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B12" s="2">
         <v>10</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2">
+      <c r="C12" s="2"/>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1">
         <v>0.50273361903901903</v>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2">
+      <c r="I12" s="1"/>
+      <c r="J12" s="1">
         <v>0.27430778792633997</v>
       </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2">
+      <c r="K12" s="1"/>
+      <c r="L12" s="1">
         <v>0.32177575521011098</v>
       </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2">
+      <c r="M12" s="1"/>
+      <c r="N12" s="1">
         <v>0.65673741494184301</v>
       </c>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-    </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="3">
+      <c r="O12" s="1"/>
+      <c r="P12" s="1">
+        <v>2.6204286313390099</v>
+      </c>
+      <c r="Q12" s="1"/>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B13" s="2">
         <v>11</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1">
+        <v>0.48671009659551501</v>
+      </c>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1">
+        <v>0.27213338601127202</v>
+      </c>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1">
+        <v>0.32550871434654999</v>
+      </c>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1">
+        <v>0.64010533192090902</v>
+      </c>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B14" s="2">
+        <v>12</v>
+      </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="100">
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
+  <mergeCells count="104">
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="P14:Q14"/>
     <mergeCell ref="P10:Q10"/>
     <mergeCell ref="N10:O10"/>
     <mergeCell ref="L10:M10"/>
@@ -895,6 +834,90 @@
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="N2:O2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 7/evals.xlsx
+++ b/Function 7/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3FFC296-DFDA-4565-AA4A-7C177976AB8D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B6129B-0B81-4E8C-BA89-3F0B13BB07DC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:Q14"/>
+  <dimension ref="B2:Q15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
@@ -789,7 +789,9 @@
         <v>0.64010533192090902</v>
       </c>
       <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
+      <c r="P13" s="1">
+        <v>2.6169964463203499</v>
+      </c>
       <c r="Q13" s="1"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
@@ -797,23 +799,141 @@
         <v>12</v>
       </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="1"/>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
       <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
       <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
+      <c r="H14" s="1">
+        <v>0.49288934693348502</v>
+      </c>
       <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
+      <c r="J14" s="1">
+        <v>0.27575262061355599</v>
+      </c>
       <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
+      <c r="L14" s="1">
+        <v>0.31373994472595101</v>
+      </c>
       <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
+      <c r="N14" s="1">
+        <v>0.65019354997019396</v>
+      </c>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
     </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="104">
+  <mergeCells count="112">
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
     <mergeCell ref="J14:K14"/>
     <mergeCell ref="L14:M14"/>
     <mergeCell ref="N14:O14"/>
@@ -834,90 +954,10 @@
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H13:I13"/>
     <mergeCell ref="J7:K7"/>
     <mergeCell ref="L7:M7"/>
     <mergeCell ref="N7:O7"/>
     <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P12:Q12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
